--- a/data/trending_integrated_20261022_09.xlsx
+++ b/data/trending_integrated_20261022_09.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z3"/>
+  <dimension ref="A1:Z7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -563,31 +563,31 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>삼성E&amp;A</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1276000</v>
+        <v>55000</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'-1.39%</t>
+          <t>'+15.30%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>0.02</v>
       </c>
       <c r="E2" t="n">
-        <v>715</v>
+        <v>86</v>
       </c>
       <c r="F2" t="n">
-        <v>459</v>
+        <v>58</v>
       </c>
       <c r="G2" t="n">
-        <v>2656</v>
+        <v>372</v>
       </c>
       <c r="H2" t="n">
-        <v>48.79</v>
+        <v>37.72</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -595,28 +595,28 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>1294000</v>
+        <v>47700</v>
       </c>
       <c r="K2" t="n">
-        <v>1273000</v>
+        <v>51000</v>
       </c>
       <c r="L2" t="n">
-        <v>1282000</v>
+        <v>55000</v>
       </c>
       <c r="M2" t="n">
-        <v>1267000</v>
+        <v>50500</v>
       </c>
       <c r="N2" t="n">
-        <v>48.77</v>
+        <v>37.7</v>
       </c>
       <c r="O2" t="n">
-        <v>166709986500</v>
+        <v>162432773500</v>
       </c>
       <c r="P2" t="n">
-        <v>2987000</v>
+        <v>67300</v>
       </c>
       <c r="Q2" t="n">
-        <v>468000</v>
+        <v>23150</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -626,20 +626,20 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>메타의 AI 투자 확대와 실적 발표 후 반도체주 상승에 대한 기대감이 있으나, 자사주 매입 종료와 솔리다임 상장 이슈 등 불확실성이 존재함.</t>
+          <t>삼성E&amp;A, 3분기 잠정 실적 어닝 서프라이즈 달성. 5천억대 영업이익 발표와 함께 6,900억 규모 자사주 소각 및 매입 결정. 주가 전망 상향 조정.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.1</v>
+        <v>0.9</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['AI 투자', '자사주 매입', '반도체주']</t>
+          <t>['실적', '자사주 소각', '어닝 서프라이즈']</t>
         </is>
       </c>
       <c r="X2" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
@@ -648,67 +648,67 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>028050</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>HLB</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>41350</v>
+        <v>225000</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'-2.36%</t>
+          <t>'+0.67%</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-0.14</v>
+        <v>0.06</v>
       </c>
       <c r="E3" t="n">
-        <v>56</v>
+        <v>669</v>
       </c>
       <c r="F3" t="n">
-        <v>39</v>
+        <v>397</v>
       </c>
       <c r="G3" t="n">
-        <v>294</v>
+        <v>2734</v>
       </c>
       <c r="H3" t="n">
-        <v>13.09</v>
+        <v>46.14</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>42350</v>
+        <v>223500</v>
       </c>
       <c r="K3" t="n">
-        <v>41850</v>
+        <v>221500</v>
       </c>
       <c r="L3" t="n">
-        <v>42350</v>
+        <v>226000</v>
       </c>
       <c r="M3" t="n">
-        <v>41350</v>
+        <v>220000</v>
       </c>
       <c r="N3" t="n">
-        <v>13.23</v>
+        <v>46.08</v>
       </c>
       <c r="O3" t="n">
-        <v>788022850</v>
+        <v>330726096500</v>
       </c>
       <c r="P3" t="n">
-        <v>69200</v>
+        <v>374500</v>
       </c>
       <c r="Q3" t="n">
-        <v>24150</v>
+        <v>94500</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
@@ -718,29 +718,397 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>HLB의 간암 치료제(C1) FDA 승인에 대한 기대감이 크나, 과거 유사 사례(리캄)의 승인 요건 미충족 및 가짜 뉴스 논란으로 인한 불확실성이 존재함.</t>
+          <t>삼성전자, 메타 호실적 및 AI 투자 확대로 인한 반도체 업황 개선 기대감. 그러나 국내 증시 움직임은 미 증시와 디커플링 양상. 25만원 목표 달성 가능성 언급.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>['반도체', 'AI', '메타']</t>
+        </is>
+      </c>
+      <c r="X3" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>005930</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>SK하이닉스</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>1296000</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>'+0.15%</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="E4" t="n">
+        <v>786</v>
+      </c>
+      <c r="F4" t="n">
+        <v>500</v>
+      </c>
+      <c r="G4" t="n">
+        <v>2776</v>
+      </c>
+      <c r="H4" t="n">
+        <v>48.79</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>1294000</v>
+      </c>
+      <c r="K4" t="n">
+        <v>1273000</v>
+      </c>
+      <c r="L4" t="n">
+        <v>1297000</v>
+      </c>
+      <c r="M4" t="n">
+        <v>1267000</v>
+      </c>
+      <c r="N4" t="n">
+        <v>48.77</v>
+      </c>
+      <c r="O4" t="n">
+        <v>391275712500</v>
+      </c>
+      <c r="P4" t="n">
+        <v>2987000</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>468000</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>메타의 AI 투자 확대와 실적 발표 후 반도체주 상승에 대한 기대감이 있으나, 자사주 매입 종료와 솔리다임 상장 이슈 등 불확실성이 존재함.</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr"/>
+      <c r="V4" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>['AI 투자', '자사주 매입', '반도체주']</t>
+        </is>
+      </c>
+      <c r="X4" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>000660</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>HLB</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>41600</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>'-1.77%</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>-0.14</v>
+      </c>
+      <c r="E5" t="n">
+        <v>72</v>
+      </c>
+      <c r="F5" t="n">
+        <v>47</v>
+      </c>
+      <c r="G5" t="n">
+        <v>327</v>
+      </c>
+      <c r="H5" t="n">
+        <v>13.09</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>42350</v>
+      </c>
+      <c r="K5" t="n">
+        <v>41850</v>
+      </c>
+      <c r="L5" t="n">
+        <v>42350</v>
+      </c>
+      <c r="M5" t="n">
+        <v>41150</v>
+      </c>
+      <c r="N5" t="n">
+        <v>13.23</v>
+      </c>
+      <c r="O5" t="n">
+        <v>2634559150</v>
+      </c>
+      <c r="P5" t="n">
+        <v>69200</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>24150</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>HLB, 간암 치료제 FDA 승인 기대감 지속. C1 등급 승인 가능성에 대한 논쟁. 공매도 세력에 대한 경고와 함께 다음 주 결과 발표 대기.</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>['HLB', 'FDA 승인', '간암']</t>
+        </is>
+      </c>
+      <c r="X5" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>028300</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>명신산업</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>9910</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>'-2.75%</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="E6" t="n">
+        <v>81</v>
+      </c>
+      <c r="F6" t="n">
+        <v>48</v>
+      </c>
+      <c r="G6" t="n">
+        <v>191</v>
+      </c>
+      <c r="H6" t="n">
+        <v>5.87</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>10190</v>
+      </c>
+      <c r="K6" t="n">
+        <v>10110</v>
+      </c>
+      <c r="L6" t="n">
+        <v>10180</v>
+      </c>
+      <c r="M6" t="n">
+        <v>9870</v>
+      </c>
+      <c r="N6" t="n">
+        <v>5.34</v>
+      </c>
+      <c r="O6" t="n">
+        <v>4170343855</v>
+      </c>
+      <c r="P6" t="n">
+        <v>14940</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>5390</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>명신산업, 테슬라 실적 상회 및 스페이스X 상장 이슈에 대한 기대감 있으나, 주가 움직임은 약세. 공매도 추정 및 재료 소멸 우려 존재.</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="n">
         <v>0.2</v>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>['FDA 승인', '간암 치료제', '공매도']</t>
-        </is>
-      </c>
-      <c r="X3" t="n">
-        <v>8</v>
-      </c>
-      <c r="Y3" t="inlineStr">
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>['테슬라', '스페이스X', '공매도']</t>
+        </is>
+      </c>
+      <c r="X6" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y6" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>028300</t>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>009900</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>HT로보틱스</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>10190</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>'-8.53%</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="E7" t="n">
+        <v>62</v>
+      </c>
+      <c r="F7" t="n">
+        <v>44</v>
+      </c>
+      <c r="G7" t="n">
+        <v>164</v>
+      </c>
+      <c r="H7" t="n">
+        <v>3.69</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>11140</v>
+      </c>
+      <c r="K7" t="n">
+        <v>10830</v>
+      </c>
+      <c r="L7" t="n">
+        <v>10880</v>
+      </c>
+      <c r="M7" t="n">
+        <v>10170</v>
+      </c>
+      <c r="N7" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="O7" t="n">
+        <v>19640046090</v>
+      </c>
+      <c r="P7" t="n">
+        <v>11690</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>2270</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>HT로보틱스, 로봇주 Nxt 시장 강세에도 불구하고 투자주의 종목 지정 및 급락. ESS 마진율 불확실성 언급. 단기 변동성 심화.</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>['로봇주', '투자주의', '급락']</t>
+        </is>
+      </c>
+      <c r="X7" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>396300</t>
         </is>
       </c>
     </row>

--- a/data/trending_integrated_20261022_09.xlsx
+++ b/data/trending_integrated_20261022_09.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z7"/>
+  <dimension ref="A1:Z10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>55000</v>
+        <v>56300</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+15.30%</t>
+          <t>'+18.03%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>0.02</v>
       </c>
       <c r="E2" t="n">
-        <v>86</v>
+        <v>113</v>
       </c>
       <c r="F2" t="n">
-        <v>58</v>
+        <v>73</v>
       </c>
       <c r="G2" t="n">
-        <v>372</v>
+        <v>477</v>
       </c>
       <c r="H2" t="n">
         <v>37.72</v>
@@ -601,7 +601,7 @@
         <v>51000</v>
       </c>
       <c r="L2" t="n">
-        <v>55000</v>
+        <v>56400</v>
       </c>
       <c r="M2" t="n">
         <v>50500</v>
@@ -610,7 +610,7 @@
         <v>37.7</v>
       </c>
       <c r="O2" t="n">
-        <v>162432773500</v>
+        <v>264399018800</v>
       </c>
       <c r="P2" t="n">
         <v>67300</v>
@@ -619,14 +619,14 @@
         <v>23150</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>836000</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>삼성E&amp;A, 3분기 잠정 실적 어닝 서프라이즈 달성. 5천억대 영업이익 발표와 함께 6,900억 규모 자사주 소각 및 매입 결정. 주가 전망 상향 조정.</t>
+          <t>실적 발표에서 어닝 서프라이즈와 주식 소각 결정, 전망 상향 등 긍정적인 공시가 연이어 발표되며 강한 상승 기대감을 나타내고 있습니다. 자사주 매입 공시도 함께 발표되어 주가 부양 의지가 강하게 반영되었습니다.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
@@ -635,7 +635,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['실적', '자사주 소각', '어닝 서프라이즈']</t>
+          <t>['어닝 서프라이즈', '주식 소각', '자사주 매입']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -655,83 +655,83 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>빅텍</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>225000</v>
+        <v>3290</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+0.67%</t>
+          <t>'+6.47%</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.06</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>669</v>
+        <v>40</v>
       </c>
       <c r="F3" t="n">
-        <v>397</v>
+        <v>30</v>
       </c>
       <c r="G3" t="n">
-        <v>2734</v>
+        <v>87</v>
       </c>
       <c r="H3" t="n">
-        <v>46.14</v>
+        <v>0</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>223500</v>
+        <v>3090</v>
       </c>
       <c r="K3" t="n">
-        <v>221500</v>
+        <v>3190</v>
       </c>
       <c r="L3" t="n">
-        <v>226000</v>
+        <v>3330</v>
       </c>
       <c r="M3" t="n">
-        <v>220000</v>
+        <v>3155</v>
       </c>
       <c r="N3" t="n">
-        <v>46.08</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>330726096500</v>
+        <v>7900223439</v>
       </c>
       <c r="P3" t="n">
-        <v>374500</v>
+        <v>7050</v>
       </c>
       <c r="Q3" t="n">
-        <v>94500</v>
+        <v>2500</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>12000</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>삼성전자, 메타 호실적 및 AI 투자 확대로 인한 반도체 업황 개선 기대감. 그러나 국내 증시 움직임은 미 증시와 디커플링 양상. 25만원 목표 달성 가능성 언급.</t>
+          <t>김정은 위원장의 신변 이상설과 전쟁 가능성에 대한 언급이 주를 이루며 이에 따른 주가 변동에 대한 기대와 우려가 혼재하고 있으나, 명확한 팩트 기반의 전망은 부족합니다.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['반도체', 'AI', '메타']</t>
+          <t>['김정은', '전쟁 가능성', '대북 확성기']</t>
         </is>
       </c>
       <c r="X3" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
@@ -740,38 +740,38 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>065450</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1296000</v>
+        <v>15090</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+0.15%</t>
+          <t>'+2.17%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.02</v>
+        <v>0.13</v>
       </c>
       <c r="E4" t="n">
-        <v>786</v>
+        <v>40</v>
       </c>
       <c r="F4" t="n">
-        <v>500</v>
+        <v>24</v>
       </c>
       <c r="G4" t="n">
-        <v>2776</v>
+        <v>93</v>
       </c>
       <c r="H4" t="n">
-        <v>48.79</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -779,38 +779,38 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>1294000</v>
+        <v>14770</v>
       </c>
       <c r="K4" t="n">
-        <v>1273000</v>
+        <v>14770</v>
       </c>
       <c r="L4" t="n">
-        <v>1297000</v>
+        <v>15290</v>
       </c>
       <c r="M4" t="n">
-        <v>1267000</v>
+        <v>14770</v>
       </c>
       <c r="N4" t="n">
-        <v>48.77</v>
+        <v>9.82</v>
       </c>
       <c r="O4" t="n">
-        <v>391275712500</v>
+        <v>14448687060</v>
       </c>
       <c r="P4" t="n">
-        <v>2987000</v>
+        <v>40350</v>
       </c>
       <c r="Q4" t="n">
-        <v>468000</v>
+        <v>3320</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>-18000</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>메타의 AI 투자 확대와 실적 발표 후 반도체주 상승에 대한 기대감이 있으나, 자사주 매입 종료와 솔리다임 상장 이슈 등 불확실성이 존재함.</t>
+          <t>종전 기대감과 외국인, 연기금의 꾸준한 매수세가 언급되지만, 정치적인 메시지가 다수 포함되어 있어 종목 자체에 대한 명확한 팩트 기반 분석은 부족합니다.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
@@ -819,7 +819,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['AI 투자', '자사주 매입', '반도체주']</t>
+          <t>['종전 기대감', '외국인 매수', '연기금']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -832,77 +832,77 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>HLB</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>41600</v>
+        <v>223000</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'-1.77%</t>
+          <t>'-0.22%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-0.14</v>
+        <v>0.06</v>
       </c>
       <c r="E5" t="n">
-        <v>72</v>
+        <v>724</v>
       </c>
       <c r="F5" t="n">
-        <v>47</v>
+        <v>421</v>
       </c>
       <c r="G5" t="n">
-        <v>327</v>
+        <v>2811</v>
       </c>
       <c r="H5" t="n">
-        <v>13.09</v>
+        <v>46.14</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>42350</v>
+        <v>223500</v>
       </c>
       <c r="K5" t="n">
-        <v>41850</v>
+        <v>221500</v>
       </c>
       <c r="L5" t="n">
-        <v>42350</v>
+        <v>226000</v>
       </c>
       <c r="M5" t="n">
-        <v>41150</v>
+        <v>220000</v>
       </c>
       <c r="N5" t="n">
-        <v>13.23</v>
+        <v>46.08</v>
       </c>
       <c r="O5" t="n">
-        <v>2634559150</v>
+        <v>430394086500</v>
       </c>
       <c r="P5" t="n">
-        <v>69200</v>
+        <v>374500</v>
       </c>
       <c r="Q5" t="n">
-        <v>24150</v>
+        <v>94500</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>-54000</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>HLB, 간암 치료제 FDA 승인 기대감 지속. C1 등급 승인 가능성에 대한 논쟁. 공매도 세력에 대한 경고와 함께 다음 주 결과 발표 대기.</t>
+          <t>삼성전자, 메타 호실적 및 AI 투자 확대로 인한 반도체 업황 개선 기대감. 그러나 국내 증시 움직임은 미 증시와 디커플링 양상. 25만원 목표 달성 가능성 언급.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
@@ -911,11 +911,11 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['HLB', 'FDA 승인', '간암']</t>
+          <t>['반도체', 'AI', '메타']</t>
         </is>
       </c>
       <c r="X5" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -924,38 +924,38 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>028300</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>명신산업</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>9910</v>
+        <v>1284000</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'-2.75%</t>
+          <t>'-0.77%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.53</v>
+        <v>0.02</v>
       </c>
       <c r="E6" t="n">
-        <v>81</v>
+        <v>800</v>
       </c>
       <c r="F6" t="n">
-        <v>48</v>
+        <v>498</v>
       </c>
       <c r="G6" t="n">
-        <v>191</v>
+        <v>2509</v>
       </c>
       <c r="H6" t="n">
-        <v>5.87</v>
+        <v>48.79</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -963,51 +963,51 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>10190</v>
+        <v>1294000</v>
       </c>
       <c r="K6" t="n">
-        <v>10110</v>
+        <v>1273000</v>
       </c>
       <c r="L6" t="n">
-        <v>10180</v>
+        <v>1297000</v>
       </c>
       <c r="M6" t="n">
-        <v>9870</v>
+        <v>1267000</v>
       </c>
       <c r="N6" t="n">
-        <v>5.34</v>
+        <v>48.77</v>
       </c>
       <c r="O6" t="n">
-        <v>4170343855</v>
+        <v>546310222000</v>
       </c>
       <c r="P6" t="n">
-        <v>14940</v>
+        <v>2987000</v>
       </c>
       <c r="Q6" t="n">
-        <v>5390</v>
+        <v>468000</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>-2000</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>명신산업, 테슬라 실적 상회 및 스페이스X 상장 이슈에 대한 기대감 있으나, 주가 움직임은 약세. 공매도 추정 및 재료 소멸 우려 존재.</t>
+          <t>메타의 AI 투자 확대 및 실적 발표 관련 뉴스가 언급되나, 경영진에 대한 비판과 자사주 매입 종료, 미 증시 움직임에 대한 의구심 등 부정적인 내용이 주를 이루고 있습니다.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['테슬라', '스페이스X', '공매도']</t>
+          <t>['AI 투자', '메타 실적', '자사주 매입 종료']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -1016,38 +1016,38 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>009900</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>HT로보틱스</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>10190</v>
+        <v>14110</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'-8.53%</t>
+          <t>'-1.40%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>2.41</v>
+        <v>0.33</v>
       </c>
       <c r="E7" t="n">
-        <v>62</v>
+        <v>46</v>
       </c>
       <c r="F7" t="n">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="G7" t="n">
-        <v>164</v>
+        <v>147</v>
       </c>
       <c r="H7" t="n">
-        <v>3.69</v>
+        <v>3.48</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1055,58 +1055,334 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>11140</v>
+        <v>14310</v>
       </c>
       <c r="K7" t="n">
-        <v>10830</v>
+        <v>14180</v>
       </c>
       <c r="L7" t="n">
-        <v>10880</v>
+        <v>14650</v>
       </c>
       <c r="M7" t="n">
-        <v>10170</v>
+        <v>13920</v>
       </c>
       <c r="N7" t="n">
-        <v>1.28</v>
+        <v>3.15</v>
       </c>
       <c r="O7" t="n">
-        <v>19640046090</v>
+        <v>27682516315</v>
       </c>
       <c r="P7" t="n">
-        <v>11690</v>
+        <v>31500</v>
       </c>
       <c r="Q7" t="n">
-        <v>2270</v>
+        <v>1640</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>-161000</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>HT로보틱스, 로봇주 Nxt 시장 강세에도 불구하고 투자주의 종목 지정 및 급락. ESS 마진율 불확실성 언급. 단기 변동성 심화.</t>
+          <t>엔비디아 AI 광통신 관련 뉴스와 해외 주요 기업의 상승세가 언급되며 긍정적인 전망이 제시되고 있으나, 나스닥 선물 및 대차 잔고에 대한 경계심도 함께 나타나고 있습니다.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>['AI 광통신', '엔비디아', '나스닥 선물']</t>
+        </is>
+      </c>
+      <c r="X7" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>010170</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>HLB</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>41400</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>'-2.24%</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>-0.14</v>
+      </c>
+      <c r="E8" t="n">
+        <v>81</v>
+      </c>
+      <c r="F8" t="n">
+        <v>50</v>
+      </c>
+      <c r="G8" t="n">
+        <v>363</v>
+      </c>
+      <c r="H8" t="n">
+        <v>13.09</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>42350</v>
+      </c>
+      <c r="K8" t="n">
+        <v>41850</v>
+      </c>
+      <c r="L8" t="n">
+        <v>42350</v>
+      </c>
+      <c r="M8" t="n">
+        <v>41150</v>
+      </c>
+      <c r="N8" t="n">
+        <v>13.23</v>
+      </c>
+      <c r="O8" t="n">
+        <v>3478270475</v>
+      </c>
+      <c r="P8" t="n">
+        <v>69200</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>24150</v>
+      </c>
+      <c r="R8" t="n">
+        <v>-1000</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>간암 신약 FDA 승인에 대한 기대감이 존재하나, 승인 여부에 대한 불확실성과 C1/C2 분류에 대한 논쟁, 공매도 세력에 대한 경고 등 다양한 의견이 엇갈리며 혼조세를 보이고 있습니다.</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>['FDA 승인', '간암 신약', '공매도']</t>
+        </is>
+      </c>
+      <c r="X8" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>028300</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>명신산업</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>9900</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>'-2.85%</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="E9" t="n">
+        <v>83</v>
+      </c>
+      <c r="F9" t="n">
+        <v>53</v>
+      </c>
+      <c r="G9" t="n">
+        <v>188</v>
+      </c>
+      <c r="H9" t="n">
+        <v>5.87</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>10190</v>
+      </c>
+      <c r="K9" t="n">
+        <v>10110</v>
+      </c>
+      <c r="L9" t="n">
+        <v>10180</v>
+      </c>
+      <c r="M9" t="n">
+        <v>9720</v>
+      </c>
+      <c r="N9" t="n">
+        <v>5.34</v>
+      </c>
+      <c r="O9" t="n">
+        <v>6255045460</v>
+      </c>
+      <c r="P9" t="n">
+        <v>14940</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>5390</v>
+      </c>
+      <c r="R9" t="n">
+        <v>-45000</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>테슬라 실적 상회 및 스페이스X 상장 이슈가 언급되나, 재료 소멸 우려와 공매도 세력에 대한 부정적인 언급이 혼재하며 변동성에 대한 기대와 우려가 공존하고 있습니다.</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>['테슬라', '스페이스X', '공매도']</t>
+        </is>
+      </c>
+      <c r="X9" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>009900</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>HT로보틱스</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>10220</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>'-8.26%</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="E10" t="n">
+        <v>76</v>
+      </c>
+      <c r="F10" t="n">
+        <v>51</v>
+      </c>
+      <c r="G10" t="n">
+        <v>198</v>
+      </c>
+      <c r="H10" t="n">
+        <v>3.69</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>11140</v>
+      </c>
+      <c r="K10" t="n">
+        <v>10830</v>
+      </c>
+      <c r="L10" t="n">
+        <v>10880</v>
+      </c>
+      <c r="M10" t="n">
+        <v>10060</v>
+      </c>
+      <c r="N10" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="O10" t="n">
+        <v>25753231520</v>
+      </c>
+      <c r="P10" t="n">
+        <v>11690</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>2270</v>
+      </c>
+      <c r="R10" t="n">
+        <v>-34000</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>로봇주로서 NXT 시장에서의 폭등 기대감이 있었으나, 투자주의 환기 종목 지정과 예상치 못한 급락 가능성에 대한 경고가 반복되며 투자 심리가 급격히 위축되고 있습니다.</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="n">
         <v>0.1</v>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>['로봇주', '투자주의', '급락']</t>
-        </is>
-      </c>
-      <c r="X7" t="n">
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>['로봇주', 'NXT 시장', '투자주의']</t>
+        </is>
+      </c>
+      <c r="X10" t="n">
         <v>5</v>
       </c>
-      <c r="Y7" t="inlineStr">
+      <c r="Y10" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
+      <c r="Z10" t="inlineStr">
         <is>
           <t>396300</t>
         </is>

--- a/data/trending_integrated_20261022_09.xlsx
+++ b/data/trending_integrated_20261022_09.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z10"/>
+  <dimension ref="A1:Z11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>56300</v>
+        <v>55100</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+18.03%</t>
+          <t>'+15.51%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>0.02</v>
       </c>
       <c r="E2" t="n">
-        <v>113</v>
+        <v>142</v>
       </c>
       <c r="F2" t="n">
-        <v>73</v>
+        <v>86</v>
       </c>
       <c r="G2" t="n">
-        <v>477</v>
+        <v>578</v>
       </c>
       <c r="H2" t="n">
         <v>37.72</v>
@@ -601,7 +601,7 @@
         <v>51000</v>
       </c>
       <c r="L2" t="n">
-        <v>56400</v>
+        <v>56500</v>
       </c>
       <c r="M2" t="n">
         <v>50500</v>
@@ -610,7 +610,7 @@
         <v>37.7</v>
       </c>
       <c r="O2" t="n">
-        <v>264399018800</v>
+        <v>311171697700</v>
       </c>
       <c r="P2" t="n">
         <v>67300</v>
@@ -626,16 +626,16 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>실적 발표에서 어닝 서프라이즈와 주식 소각 결정, 전망 상향 등 긍정적인 공시가 연이어 발표되며 강한 상승 기대감을 나타내고 있습니다. 자사주 매입 공시도 함께 발표되어 주가 부양 의지가 강하게 반영되었습니다.</t>
+          <t>삼성E&amp;A, 실적 발표서 어닝 서프라이즈 기록 및 주식 소각 결정. 전망 상향 및 자사주 취득 공시.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['어닝 서프라이즈', '주식 소각', '자사주 매입']</t>
+          <t>['어닝 서프라이즈', '주식 소각', '자사주 취득']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3290</v>
+        <v>3330</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+6.47%</t>
+          <t>'+7.77%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="F3" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G3" t="n">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -693,7 +693,7 @@
         <v>3190</v>
       </c>
       <c r="L3" t="n">
-        <v>3330</v>
+        <v>3400</v>
       </c>
       <c r="M3" t="n">
         <v>3155</v>
@@ -702,7 +702,7 @@
         <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>7900223439</v>
+        <v>12263204995</v>
       </c>
       <c r="P3" t="n">
         <v>7050</v>
@@ -718,16 +718,16 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>김정은 위원장의 신변 이상설과 전쟁 가능성에 대한 언급이 주를 이루며 이에 따른 주가 변동에 대한 기대와 우려가 혼재하고 있으나, 명확한 팩트 기반의 전망은 부족합니다.</t>
+          <t>빅텍, 김정은 신변 이상설 및 전쟁 가능성 관련 언급. 급등 및 변동성 시현.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['김정은', '전쟁 가능성', '대북 확성기']</t>
+          <t>['김정은', '전쟁 가능성', '급등']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -747,83 +747,83 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>푸드나무</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>15090</v>
+        <v>1650</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+2.17%</t>
+          <t>'+2.48%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.13</v>
+        <v>-0.39</v>
       </c>
       <c r="E4" t="n">
         <v>40</v>
       </c>
       <c r="F4" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="G4" t="n">
-        <v>93</v>
+        <v>74</v>
       </c>
       <c r="H4" t="n">
-        <v>9.949999999999999</v>
+        <v>0.3</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>14770</v>
+        <v>1610</v>
       </c>
       <c r="K4" t="n">
-        <v>14770</v>
+        <v>1655</v>
       </c>
       <c r="L4" t="n">
-        <v>15290</v>
+        <v>1780</v>
       </c>
       <c r="M4" t="n">
-        <v>14770</v>
+        <v>1622</v>
       </c>
       <c r="N4" t="n">
-        <v>9.82</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="O4" t="n">
-        <v>14448687060</v>
+        <v>4841098805</v>
       </c>
       <c r="P4" t="n">
-        <v>40350</v>
+        <v>3980</v>
       </c>
       <c r="Q4" t="n">
-        <v>3320</v>
+        <v>1115</v>
       </c>
       <c r="R4" t="n">
-        <v>-18000</v>
+        <v>14000</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>종전 기대감과 외국인, 연기금의 꾸준한 매수세가 언급되지만, 정치적인 메시지가 다수 포함되어 있어 종목 자체에 대한 명확한 팩트 기반 분석은 부족합니다.</t>
+          <t>푸드나무, 연속 하한가 발생 후 경영권 인수 가능성 언급. 주가 조작 및 상장폐지 관련 논의.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['종전 기대감', '외국인 매수', '연기금']</t>
+          <t>['하한가', '경영권 인수', '주가 조작']</t>
         </is>
       </c>
       <c r="X4" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
@@ -832,38 +832,38 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>290720</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>223000</v>
+        <v>15010</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'-0.22%</t>
+          <t>'+1.62%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.06</v>
+        <v>0.13</v>
       </c>
       <c r="E5" t="n">
-        <v>724</v>
+        <v>42</v>
       </c>
       <c r="F5" t="n">
-        <v>421</v>
+        <v>24</v>
       </c>
       <c r="G5" t="n">
-        <v>2811</v>
+        <v>108</v>
       </c>
       <c r="H5" t="n">
-        <v>46.14</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -871,47 +871,47 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>223500</v>
+        <v>14770</v>
       </c>
       <c r="K5" t="n">
-        <v>221500</v>
+        <v>14770</v>
       </c>
       <c r="L5" t="n">
-        <v>226000</v>
+        <v>15290</v>
       </c>
       <c r="M5" t="n">
-        <v>220000</v>
+        <v>14770</v>
       </c>
       <c r="N5" t="n">
-        <v>46.08</v>
+        <v>9.82</v>
       </c>
       <c r="O5" t="n">
-        <v>430394086500</v>
+        <v>16946634635</v>
       </c>
       <c r="P5" t="n">
-        <v>374500</v>
+        <v>40350</v>
       </c>
       <c r="Q5" t="n">
-        <v>94500</v>
+        <v>3320</v>
       </c>
       <c r="R5" t="n">
-        <v>-54000</v>
+        <v>-18000</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>삼성전자, 메타 호실적 및 AI 투자 확대로 인한 반도체 업황 개선 기대감. 그러나 국내 증시 움직임은 미 증시와 디커플링 양상. 25만원 목표 달성 가능성 언급.</t>
+          <t>대우건설, 외국인 및 연기금 매수세 확인. 일부 투자자, 정치적 이슈와 주가 관련 언급.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['반도체', 'AI', '메타']</t>
+          <t>['외국인 매수', '연기금', '실적 우량주']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -924,38 +924,38 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1284000</v>
+        <v>220750</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'-0.77%</t>
+          <t>'-1.23%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.02</v>
+        <v>0.06</v>
       </c>
       <c r="E6" t="n">
-        <v>800</v>
+        <v>772</v>
       </c>
       <c r="F6" t="n">
-        <v>498</v>
+        <v>443</v>
       </c>
       <c r="G6" t="n">
-        <v>2509</v>
+        <v>2943</v>
       </c>
       <c r="H6" t="n">
-        <v>48.79</v>
+        <v>46.14</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -963,47 +963,47 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>1294000</v>
+        <v>223500</v>
       </c>
       <c r="K6" t="n">
-        <v>1273000</v>
+        <v>221500</v>
       </c>
       <c r="L6" t="n">
-        <v>1297000</v>
+        <v>226000</v>
       </c>
       <c r="M6" t="n">
-        <v>1267000</v>
+        <v>220000</v>
       </c>
       <c r="N6" t="n">
-        <v>48.77</v>
+        <v>46.08</v>
       </c>
       <c r="O6" t="n">
-        <v>546310222000</v>
+        <v>509144556000</v>
       </c>
       <c r="P6" t="n">
-        <v>2987000</v>
+        <v>374500</v>
       </c>
       <c r="Q6" t="n">
-        <v>468000</v>
+        <v>94500</v>
       </c>
       <c r="R6" t="n">
-        <v>-2000</v>
+        <v>-54000</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>메타의 AI 투자 확대 및 실적 발표 관련 뉴스가 언급되나, 경영진에 대한 비판과 자사주 매입 종료, 미 증시 움직임에 대한 의구심 등 부정적인 내용이 주를 이루고 있습니다.</t>
+          <t>삼성전자, 메타 호실적 및 AI 투자 확대로 인한 반도체 업황 개선 기대감. 그러나 국내 증시 움직임은 미 증시와 디커플링 양상. 25만원 목표 달성 가능성 언급.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['AI 투자', '메타 실적', '자사주 매입 종료']</t>
+          <t>['반도체', 'AI', '메타']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1016,7 +1016,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
@@ -1027,24 +1027,24 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>14110</v>
+        <v>14080</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'-1.40%</t>
+          <t>'-1.61%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>0.33</v>
       </c>
       <c r="E7" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F7" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G7" t="n">
-        <v>147</v>
+        <v>182</v>
       </c>
       <c r="H7" t="n">
         <v>3.48</v>
@@ -1064,13 +1064,13 @@
         <v>14650</v>
       </c>
       <c r="M7" t="n">
-        <v>13920</v>
+        <v>13890</v>
       </c>
       <c r="N7" t="n">
         <v>3.15</v>
       </c>
       <c r="O7" t="n">
-        <v>27682516315</v>
+        <v>33215018410</v>
       </c>
       <c r="P7" t="n">
         <v>31500</v>
@@ -1086,16 +1086,16 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>엔비디아 AI 광통신 관련 뉴스와 해외 주요 기업의 상승세가 언급되며 긍정적인 전망이 제시되고 있으나, 나스닥 선물 및 대차 잔고에 대한 경계심도 함께 나타나고 있습니다.</t>
+          <t>대한광통신, AI 광통신 관련 뉴스 및 기술주 동향 언급. 대차 잔고 증가 및 주가 변동성.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['AI 광통신', '엔비디아', '나스닥 선물']</t>
+          <t>['AI 광통신', '기술주', '대차 잔고']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1115,83 +1115,83 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>HLB</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>41400</v>
+        <v>1270000</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'-2.24%</t>
+          <t>'-1.85%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-0.14</v>
+        <v>0.02</v>
       </c>
       <c r="E8" t="n">
-        <v>81</v>
+        <v>800</v>
       </c>
       <c r="F8" t="n">
-        <v>50</v>
+        <v>495</v>
       </c>
       <c r="G8" t="n">
-        <v>363</v>
+        <v>2245</v>
       </c>
       <c r="H8" t="n">
-        <v>13.09</v>
+        <v>48.79</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>42350</v>
+        <v>1294000</v>
       </c>
       <c r="K8" t="n">
-        <v>41850</v>
+        <v>1273000</v>
       </c>
       <c r="L8" t="n">
-        <v>42350</v>
+        <v>1297000</v>
       </c>
       <c r="M8" t="n">
-        <v>41150</v>
+        <v>1267000</v>
       </c>
       <c r="N8" t="n">
-        <v>13.23</v>
+        <v>48.77</v>
       </c>
       <c r="O8" t="n">
-        <v>3478270475</v>
+        <v>600045971000</v>
       </c>
       <c r="P8" t="n">
-        <v>69200</v>
+        <v>2987000</v>
       </c>
       <c r="Q8" t="n">
-        <v>24150</v>
+        <v>468000</v>
       </c>
       <c r="R8" t="n">
-        <v>-1000</v>
+        <v>-2000</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>간암 신약 FDA 승인에 대한 기대감이 존재하나, 승인 여부에 대한 불확실성과 C1/C2 분류에 대한 논쟁, 공매도 세력에 대한 경고 등 다양한 의견이 엇갈리며 혼조세를 보이고 있습니다.</t>
+          <t>SK하이닉스, 메타 실적 발표 및 미 반도체주 상승 언급. 자사주 매입 종료 및 경영진 관련 부정적 의견.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['FDA 승인', '간암 신약', '공매도']</t>
+          <t>['메타 실적', '자사주 매입', '반도체주']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -1200,90 +1200,90 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>028300</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>명신산업</t>
+          <t>HLB</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>9900</v>
+        <v>41300</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'-2.85%</t>
+          <t>'-2.48%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.53</v>
+        <v>-0.14</v>
       </c>
       <c r="E9" t="n">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="F9" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="G9" t="n">
-        <v>188</v>
+        <v>418</v>
       </c>
       <c r="H9" t="n">
-        <v>5.87</v>
+        <v>13.09</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>10190</v>
+        <v>42350</v>
       </c>
       <c r="K9" t="n">
-        <v>10110</v>
+        <v>41850</v>
       </c>
       <c r="L9" t="n">
-        <v>10180</v>
+        <v>42350</v>
       </c>
       <c r="M9" t="n">
-        <v>9720</v>
+        <v>41150</v>
       </c>
       <c r="N9" t="n">
-        <v>5.34</v>
+        <v>13.23</v>
       </c>
       <c r="O9" t="n">
-        <v>6255045460</v>
+        <v>4110802725</v>
       </c>
       <c r="P9" t="n">
-        <v>14940</v>
+        <v>69200</v>
       </c>
       <c r="Q9" t="n">
-        <v>5390</v>
+        <v>24150</v>
       </c>
       <c r="R9" t="n">
-        <v>-45000</v>
+        <v>-1000</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>테슬라 실적 상회 및 스페이스X 상장 이슈가 언급되나, 재료 소멸 우려와 공매도 세력에 대한 부정적인 언급이 혼재하며 변동성에 대한 기대와 우려가 공존하고 있습니다.</t>
+          <t>HLB, 간암 치료제 FDA 승인 기대감 및 공매도 관련 논의. 기관 수급 및 C1/C2 관련 분석.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['테슬라', '스페이스X', '공매도']</t>
+          <t>['FDA 승인', '간암 치료제', '공매도']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -1292,97 +1292,189 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>009900</t>
+          <t>028300</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>HT로보틱스</t>
+          <t>명신산업</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>10220</v>
+        <v>9890</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'-8.26%</t>
+          <t>'-2.94%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>2.41</v>
+        <v>0.53</v>
       </c>
       <c r="E10" t="n">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="F10" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="G10" t="n">
-        <v>198</v>
+        <v>234</v>
       </c>
       <c r="H10" t="n">
-        <v>3.69</v>
+        <v>5.87</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>11140</v>
+        <v>10190</v>
       </c>
       <c r="K10" t="n">
-        <v>10830</v>
+        <v>10110</v>
       </c>
       <c r="L10" t="n">
-        <v>10880</v>
+        <v>10180</v>
       </c>
       <c r="M10" t="n">
-        <v>10060</v>
+        <v>9720</v>
       </c>
       <c r="N10" t="n">
-        <v>1.28</v>
+        <v>5.34</v>
       </c>
       <c r="O10" t="n">
-        <v>25753231520</v>
+        <v>7003657215</v>
       </c>
       <c r="P10" t="n">
-        <v>11690</v>
+        <v>14940</v>
       </c>
       <c r="Q10" t="n">
-        <v>2270</v>
+        <v>5390</v>
       </c>
       <c r="R10" t="n">
-        <v>-34000</v>
+        <v>-45000</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>로봇주로서 NXT 시장에서의 폭등 기대감이 있었으나, 투자주의 환기 종목 지정과 예상치 못한 급락 가능성에 대한 경고가 반복되며 투자 심리가 급격히 위축되고 있습니다.</t>
+          <t>명신산업, 테슬라 실적 호조 및 스페이스X 이슈 언급. 외국인 보유율 변화 및 공매도 관련 논의.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['로봇주', 'NXT 시장', '투자주의']</t>
+          <t>['테슬라', '스페이스X', '공매도']</t>
         </is>
       </c>
       <c r="X10" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>009900</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>HT로보틱스</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>10160</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>'-8.80%</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="E11" t="n">
+        <v>88</v>
+      </c>
+      <c r="F11" t="n">
+        <v>57</v>
+      </c>
+      <c r="G11" t="n">
+        <v>231</v>
+      </c>
+      <c r="H11" t="n">
+        <v>3.69</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>11140</v>
+      </c>
+      <c r="K11" t="n">
+        <v>10830</v>
+      </c>
+      <c r="L11" t="n">
+        <v>10880</v>
+      </c>
+      <c r="M11" t="n">
+        <v>10050</v>
+      </c>
+      <c r="N11" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="O11" t="n">
+        <v>29496567590</v>
+      </c>
+      <c r="P11" t="n">
+        <v>11690</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>2270</v>
+      </c>
+      <c r="R11" t="n">
+        <v>-34000</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>HT로보틱스, 로봇주 급등 후 급락 및 투자주의 예고. ESS 마진율 불확실성 및 개인 투자자 동향.</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>['로봇주', '투자주의', '급락']</t>
+        </is>
+      </c>
+      <c r="X11" t="n">
         <v>5</v>
       </c>
-      <c r="Y10" t="inlineStr">
+      <c r="Y11" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
+      <c r="Z11" t="inlineStr">
         <is>
           <t>396300</t>
         </is>

--- a/data/trending_integrated_20261022_09.xlsx
+++ b/data/trending_integrated_20261022_09.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z11"/>
+  <dimension ref="A1:Z12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>55100</v>
+        <v>54800</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+15.51%</t>
+          <t>'+14.88%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>0.02</v>
       </c>
       <c r="E2" t="n">
-        <v>142</v>
+        <v>154</v>
       </c>
       <c r="F2" t="n">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="G2" t="n">
-        <v>578</v>
+        <v>621</v>
       </c>
       <c r="H2" t="n">
         <v>37.72</v>
@@ -610,7 +610,7 @@
         <v>37.7</v>
       </c>
       <c r="O2" t="n">
-        <v>311171697700</v>
+        <v>334501922900</v>
       </c>
       <c r="P2" t="n">
         <v>67300</v>
@@ -626,16 +626,16 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>삼성E&amp;A, 실적 발표서 어닝 서프라이즈 기록 및 주식 소각 결정. 전망 상향 및 자사주 취득 공시.</t>
+          <t>실적 발표, 어닝 서프라이즈 및 주식 소각 결정, 전망 상향, 자사주 매입 공시 등 다수의 긍정적 요인이 복합적으로 작용하며 강한 상승세를 보임.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['어닝 서프라이즈', '주식 소각', '자사주 취득']</t>
+          <t>['어닝 서프라이즈', '주식 소각', '자사주 매입']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3330</v>
+        <v>3350</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+7.77%</t>
+          <t>'+8.41%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="F3" t="n">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="G3" t="n">
-        <v>98</v>
+        <v>111</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -702,7 +702,7 @@
         <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>12263204995</v>
+        <v>13692486478</v>
       </c>
       <c r="P3" t="n">
         <v>7050</v>
@@ -718,16 +718,16 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>빅텍, 김정은 신변 이상설 및 전쟁 가능성 관련 언급. 급등 및 변동성 시현.</t>
+          <t>김정은 신변 이상설 및 전쟁 가능성 고조에 따른 테마주로서 급등세를 보이며, 관련 뉴스와 함께 투기적 수요 유입.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['김정은', '전쟁 가능성', '급등']</t>
+          <t>['김정은 신변 이상설', '전쟁 테마', '급등']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -747,70 +747,70 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>푸드나무</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1650</v>
+        <v>15090</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+2.48%</t>
+          <t>'+2.17%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-0.39</v>
+        <v>0.13</v>
       </c>
       <c r="E4" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="F4" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="G4" t="n">
-        <v>74</v>
+        <v>117</v>
       </c>
       <c r="H4" t="n">
-        <v>0.3</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>1610</v>
+        <v>14770</v>
       </c>
       <c r="K4" t="n">
-        <v>1655</v>
+        <v>14770</v>
       </c>
       <c r="L4" t="n">
-        <v>1780</v>
+        <v>15290</v>
       </c>
       <c r="M4" t="n">
-        <v>1622</v>
+        <v>14770</v>
       </c>
       <c r="N4" t="n">
-        <v>0.6899999999999999</v>
+        <v>9.82</v>
       </c>
       <c r="O4" t="n">
-        <v>4841098805</v>
+        <v>18122158975</v>
       </c>
       <c r="P4" t="n">
-        <v>3980</v>
+        <v>40350</v>
       </c>
       <c r="Q4" t="n">
-        <v>1115</v>
+        <v>3320</v>
       </c>
       <c r="R4" t="n">
-        <v>14000</v>
+        <v>-18000</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>푸드나무, 연속 하한가 발생 후 경영권 인수 가능성 언급. 주가 조작 및 상장폐지 관련 논의.</t>
+          <t>외국인 및 연기금의 꾸준한 매수세와 실적 우량주라는 언급이 있으나, 정치적 이슈 언급이 다수이며 주가 상승에 대한 명확한 근거 제시 부족.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
@@ -819,11 +819,11 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['하한가', '경영권 인수', '주가 조작']</t>
+          <t>['외국인 매수', '실적 우량주', '정치적 이슈']</t>
         </is>
       </c>
       <c r="X4" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
@@ -832,90 +832,90 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>290720</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>푸드나무</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>15010</v>
+        <v>1637</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+1.62%</t>
+          <t>'+1.68%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.13</v>
+        <v>-0.39</v>
       </c>
       <c r="E5" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F5" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="G5" t="n">
-        <v>108</v>
+        <v>80</v>
       </c>
       <c r="H5" t="n">
-        <v>9.949999999999999</v>
+        <v>0.3</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>14770</v>
+        <v>1610</v>
       </c>
       <c r="K5" t="n">
-        <v>14770</v>
+        <v>1655</v>
       </c>
       <c r="L5" t="n">
-        <v>15290</v>
+        <v>1780</v>
       </c>
       <c r="M5" t="n">
-        <v>14770</v>
+        <v>1622</v>
       </c>
       <c r="N5" t="n">
-        <v>9.82</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="O5" t="n">
-        <v>16946634635</v>
+        <v>5181946511</v>
       </c>
       <c r="P5" t="n">
-        <v>40350</v>
+        <v>3980</v>
       </c>
       <c r="Q5" t="n">
-        <v>3320</v>
+        <v>1115</v>
       </c>
       <c r="R5" t="n">
-        <v>-18000</v>
+        <v>14000</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>대우건설, 외국인 및 연기금 매수세 확인. 일부 투자자, 정치적 이슈와 주가 관련 언급.</t>
+          <t>이유 없는 하한가 두 번에 대한 의문 제기 및 주가 조작 의혹이 제기되며, 매각 불확정성 등 불확실성이 커 투자 심리 위축.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['외국인 매수', '연기금', '실적 우량주']</t>
+          <t>['하한가', '주가 조작', '매각 불확정성']</t>
         </is>
       </c>
       <c r="X5" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -924,90 +924,90 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>290720</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>220750</v>
+        <v>14520</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'-1.23%</t>
+          <t>'+1.47%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.06</v>
+        <v>0.33</v>
       </c>
       <c r="E6" t="n">
-        <v>772</v>
+        <v>51</v>
       </c>
       <c r="F6" t="n">
-        <v>443</v>
+        <v>35</v>
       </c>
       <c r="G6" t="n">
-        <v>2943</v>
+        <v>187</v>
       </c>
       <c r="H6" t="n">
-        <v>46.14</v>
+        <v>3.48</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>223500</v>
+        <v>14310</v>
       </c>
       <c r="K6" t="n">
-        <v>221500</v>
+        <v>14180</v>
       </c>
       <c r="L6" t="n">
-        <v>226000</v>
+        <v>14650</v>
       </c>
       <c r="M6" t="n">
-        <v>220000</v>
+        <v>13890</v>
       </c>
       <c r="N6" t="n">
-        <v>46.08</v>
+        <v>3.15</v>
       </c>
       <c r="O6" t="n">
-        <v>509144556000</v>
+        <v>37786996550</v>
       </c>
       <c r="P6" t="n">
-        <v>374500</v>
+        <v>31500</v>
       </c>
       <c r="Q6" t="n">
-        <v>94500</v>
+        <v>1640</v>
       </c>
       <c r="R6" t="n">
-        <v>-54000</v>
+        <v>-161000</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>삼성전자, 메타 호실적 및 AI 투자 확대로 인한 반도체 업황 개선 기대감. 그러나 국내 증시 움직임은 미 증시와 디커플링 양상. 25만원 목표 달성 가능성 언급.</t>
+          <t>엔비디아 AI 광통신 관련 글로벌 열풍 및 긍정적 뉴스 언급으로 인한 기대감이 형성되었으나, 나스닥 선물 변동성과 대차 잔고 부담으로 상승 동력 약화.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['반도체', 'AI', '메타']</t>
+          <t>['AI 광통신', '엔비디아', '대차 잔고']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -1016,90 +1016,90 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>14080</v>
+        <v>221500</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'-1.61%</t>
+          <t>'-0.89%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.33</v>
+        <v>0.06</v>
       </c>
       <c r="E7" t="n">
-        <v>48</v>
+        <v>800</v>
       </c>
       <c r="F7" t="n">
-        <v>34</v>
+        <v>460</v>
       </c>
       <c r="G7" t="n">
-        <v>182</v>
+        <v>2877</v>
       </c>
       <c r="H7" t="n">
-        <v>3.48</v>
+        <v>46.14</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>14310</v>
+        <v>223500</v>
       </c>
       <c r="K7" t="n">
-        <v>14180</v>
+        <v>221500</v>
       </c>
       <c r="L7" t="n">
-        <v>14650</v>
+        <v>226000</v>
       </c>
       <c r="M7" t="n">
-        <v>13890</v>
+        <v>220000</v>
       </c>
       <c r="N7" t="n">
-        <v>3.15</v>
+        <v>46.08</v>
       </c>
       <c r="O7" t="n">
-        <v>33215018410</v>
+        <v>553961994000</v>
       </c>
       <c r="P7" t="n">
-        <v>31500</v>
+        <v>374500</v>
       </c>
       <c r="Q7" t="n">
-        <v>1640</v>
+        <v>94500</v>
       </c>
       <c r="R7" t="n">
-        <v>-161000</v>
+        <v>-54000</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>대한광통신, AI 광통신 관련 뉴스 및 기술주 동향 언급. 대차 잔고 증가 및 주가 변동성.</t>
+          <t>메타 호실적 및 AI 투자 확대 기대감과 달리, 반도체 섹터 전반의 혼조세 및 외국인 매매 패턴에 따라 변동성이 큰 모습을 보이며, 뚜렷한 방향성 없이 등락을 반복.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['AI 광통신', '기술주', '대차 잔고']</t>
+          <t>['AI 투자', '반도체 섹터', '외국인 매매']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1108,38 +1108,38 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>LG디스플레이</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1270000</v>
+        <v>7250</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'-1.85%</t>
+          <t>'-1.36%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>0.02</v>
       </c>
       <c r="E8" t="n">
-        <v>800</v>
+        <v>40</v>
       </c>
       <c r="F8" t="n">
-        <v>495</v>
+        <v>25</v>
       </c>
       <c r="G8" t="n">
-        <v>2245</v>
+        <v>111</v>
       </c>
       <c r="H8" t="n">
-        <v>48.79</v>
+        <v>25.47</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1147,51 +1147,51 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>1294000</v>
+        <v>7350</v>
       </c>
       <c r="K8" t="n">
-        <v>1273000</v>
+        <v>7270</v>
       </c>
       <c r="L8" t="n">
-        <v>1297000</v>
+        <v>7340</v>
       </c>
       <c r="M8" t="n">
-        <v>1267000</v>
+        <v>7210</v>
       </c>
       <c r="N8" t="n">
-        <v>48.77</v>
+        <v>25.45</v>
       </c>
       <c r="O8" t="n">
-        <v>600045971000</v>
+        <v>3493800555</v>
       </c>
       <c r="P8" t="n">
-        <v>2987000</v>
+        <v>17950</v>
       </c>
       <c r="Q8" t="n">
-        <v>468000</v>
+        <v>7190</v>
       </c>
       <c r="R8" t="n">
-        <v>-2000</v>
+        <v>-20000</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>SK하이닉스, 메타 실적 발표 및 미 반도체주 상승 언급. 자사주 매입 종료 및 경영진 관련 부정적 의견.</t>
+          <t>실적 발표에 따른 폭락 및 향후 전망에 대한 불확실성으로 투자 심리가 극도로 위축되었으며, PBR 지표와 기대감 언급에도 불구하고 매도 압력 지속.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['메타 실적', '자사주 매입', '반도체주']</t>
+          <t>['실적 발표', '향후 전망', 'PBR']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -1200,90 +1200,90 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>034220</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>HLB</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>41300</v>
+        <v>1276000</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'-2.48%</t>
+          <t>'-1.39%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-0.14</v>
+        <v>0.02</v>
       </c>
       <c r="E9" t="n">
-        <v>90</v>
+        <v>800</v>
       </c>
       <c r="F9" t="n">
-        <v>55</v>
+        <v>494</v>
       </c>
       <c r="G9" t="n">
-        <v>418</v>
+        <v>2008</v>
       </c>
       <c r="H9" t="n">
-        <v>13.09</v>
+        <v>48.79</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>42350</v>
+        <v>1294000</v>
       </c>
       <c r="K9" t="n">
-        <v>41850</v>
+        <v>1273000</v>
       </c>
       <c r="L9" t="n">
-        <v>42350</v>
+        <v>1297000</v>
       </c>
       <c r="M9" t="n">
-        <v>41150</v>
+        <v>1267000</v>
       </c>
       <c r="N9" t="n">
-        <v>13.23</v>
+        <v>48.77</v>
       </c>
       <c r="O9" t="n">
-        <v>4110802725</v>
+        <v>662249335000</v>
       </c>
       <c r="P9" t="n">
-        <v>69200</v>
+        <v>2987000</v>
       </c>
       <c r="Q9" t="n">
-        <v>24150</v>
+        <v>468000</v>
       </c>
       <c r="R9" t="n">
-        <v>-1000</v>
+        <v>-2000</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>HLB, 간암 치료제 FDA 승인 기대감 및 공매도 관련 논의. 기관 수급 및 C1/C2 관련 분석.</t>
+          <t>자사주 매입 종료와 미국장 반도체 주가 변동성에 대한 우려, 정치적 리스크 언급 등으로 인해 투자 심리가 위축되며 하락세를 보이고, 뚜렷한 호재 부재.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['FDA 승인', '간암 치료제', '공매도']</t>
+          <t>['자사주 매입 종료', '반도체 주가', '정치적 리스크']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -1292,90 +1292,90 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>028300</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>명신산업</t>
+          <t>HLB</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>9890</v>
+        <v>41450</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'-2.94%</t>
+          <t>'-2.13%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.53</v>
+        <v>-0.14</v>
       </c>
       <c r="E10" t="n">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="F10" t="n">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="G10" t="n">
-        <v>234</v>
+        <v>431</v>
       </c>
       <c r="H10" t="n">
-        <v>5.87</v>
+        <v>13.09</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>10190</v>
+        <v>42350</v>
       </c>
       <c r="K10" t="n">
-        <v>10110</v>
+        <v>41850</v>
       </c>
       <c r="L10" t="n">
-        <v>10180</v>
+        <v>42350</v>
       </c>
       <c r="M10" t="n">
-        <v>9720</v>
+        <v>41150</v>
       </c>
       <c r="N10" t="n">
-        <v>5.34</v>
+        <v>13.23</v>
       </c>
       <c r="O10" t="n">
-        <v>7003657215</v>
+        <v>4406933325</v>
       </c>
       <c r="P10" t="n">
-        <v>14940</v>
+        <v>69200</v>
       </c>
       <c r="Q10" t="n">
-        <v>5390</v>
+        <v>24150</v>
       </c>
       <c r="R10" t="n">
-        <v>-45000</v>
+        <v>-1000</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>명신산업, 테슬라 실적 호조 및 스페이스X 이슈 언급. 외국인 보유율 변화 및 공매도 관련 논의.</t>
+          <t>HLB, 간암 치료제 FDA 승인 기대감 및 공매도 관련 논의. 기관 수급 및 C1/C2 관련 분석.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['테슬라', '스페이스X', '공매도']</t>
+          <t>['FDA 승인', '간암 치료제', '공매도']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1384,97 +1384,189 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>009900</t>
+          <t>028300</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>HT로보틱스</t>
+          <t>명신산업</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>10160</v>
+        <v>9820</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-8.80%</t>
+          <t>'-3.63%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>2.41</v>
+        <v>0.53</v>
       </c>
       <c r="E11" t="n">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="F11" t="n">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G11" t="n">
-        <v>231</v>
+        <v>242</v>
       </c>
       <c r="H11" t="n">
-        <v>3.69</v>
+        <v>5.87</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>11140</v>
+        <v>10190</v>
       </c>
       <c r="K11" t="n">
-        <v>10830</v>
+        <v>10110</v>
       </c>
       <c r="L11" t="n">
-        <v>10880</v>
+        <v>10180</v>
       </c>
       <c r="M11" t="n">
-        <v>10050</v>
+        <v>9720</v>
       </c>
       <c r="N11" t="n">
-        <v>1.28</v>
+        <v>5.34</v>
       </c>
       <c r="O11" t="n">
-        <v>29496567590</v>
+        <v>7349378405</v>
       </c>
       <c r="P11" t="n">
-        <v>11690</v>
+        <v>14940</v>
       </c>
       <c r="Q11" t="n">
-        <v>2270</v>
+        <v>5390</v>
       </c>
       <c r="R11" t="n">
-        <v>-34000</v>
+        <v>-45000</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>HT로보틱스, 로봇주 급등 후 급락 및 투자주의 예고. ESS 마진율 불확실성 및 개인 투자자 동향.</t>
+          <t>테슬라 실적 상회 및 스페이스X 상장 이슈 등 긍정적 재료 언급에도 불구하고, 공매도 압박 및 변동성 심화로 인해 하락세를 보이며 투자 심리 위축.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>['테슬라 실적', '공매도', '변동성']</t>
+        </is>
+      </c>
+      <c r="X11" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>009900</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>HT로보틱스</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>10340</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>'-7.18%</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="E12" t="n">
+        <v>88</v>
+      </c>
+      <c r="F12" t="n">
+        <v>57</v>
+      </c>
+      <c r="G12" t="n">
+        <v>250</v>
+      </c>
+      <c r="H12" t="n">
+        <v>3.69</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>11140</v>
+      </c>
+      <c r="K12" t="n">
+        <v>10830</v>
+      </c>
+      <c r="L12" t="n">
+        <v>10880</v>
+      </c>
+      <c r="M12" t="n">
+        <v>10050</v>
+      </c>
+      <c r="N12" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="O12" t="n">
+        <v>31457845550</v>
+      </c>
+      <c r="P12" t="n">
+        <v>11690</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>2270</v>
+      </c>
+      <c r="R12" t="n">
+        <v>-34000</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>로봇주 Nxt 시장 폭등 기대감에도 불구하고, 예상치 못한 투기 과열 지정 및 ESS 마진율 불확실성 등으로 급락하며 투자 심리 급랭.</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="n">
         <v>0.3</v>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>['로봇주', '투자주의', '급락']</t>
-        </is>
-      </c>
-      <c r="X11" t="n">
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>['로봇주', '투기 과열', 'ESS 마진율']</t>
+        </is>
+      </c>
+      <c r="X12" t="n">
         <v>5</v>
       </c>
-      <c r="Y11" t="inlineStr">
+      <c r="Y12" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
+      <c r="Z12" t="inlineStr">
         <is>
           <t>396300</t>
         </is>

--- a/data/trending_integrated_20261022_09.xlsx
+++ b/data/trending_integrated_20261022_09.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z12"/>
+  <dimension ref="A1:Z13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -563,31 +563,31 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>삼성E&amp;A</t>
+          <t>유니켐</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>54800</v>
+        <v>7810</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+14.88%</t>
+          <t>'+17.27%</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>154</v>
+        <v>43</v>
       </c>
       <c r="F2" t="n">
-        <v>94</v>
+        <v>17</v>
       </c>
       <c r="G2" t="n">
-        <v>621</v>
+        <v>41</v>
       </c>
       <c r="H2" t="n">
-        <v>37.72</v>
+        <v>0</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -595,47 +595,47 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>47700</v>
+        <v>6660</v>
       </c>
       <c r="K2" t="n">
-        <v>51000</v>
+        <v>6710</v>
       </c>
       <c r="L2" t="n">
-        <v>56500</v>
+        <v>8430</v>
       </c>
       <c r="M2" t="n">
-        <v>50500</v>
+        <v>6640</v>
       </c>
       <c r="N2" t="n">
-        <v>37.7</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>334501922900</v>
+        <v>5409116510</v>
       </c>
       <c r="P2" t="n">
-        <v>67300</v>
+        <v>8430</v>
       </c>
       <c r="Q2" t="n">
-        <v>23150</v>
+        <v>391</v>
       </c>
       <c r="R2" t="n">
-        <v>836000</v>
+        <v>14000</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>실적 발표, 어닝 서프라이즈 및 주식 소각 결정, 전망 상향, 자사주 매입 공시 등 다수의 긍정적 요인이 복합적으로 작용하며 강한 상승세를 보임.</t>
+          <t>휴머노이드 로봇 관련 기술 개발 및 미국 기업 인수 기대감. 루미아 전자장갑 설계 완성.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['어닝 서프라이즈', '주식 소각', '자사주 매입']</t>
+          <t>['휴머노이드 로봇', '루미아', '전자장갑']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -648,90 +648,90 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>028050</t>
+          <t>011330</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>빅텍</t>
+          <t>삼성E&amp;A</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3350</v>
+        <v>55200</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+8.41%</t>
+          <t>'+15.72%</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="E3" t="n">
-        <v>54</v>
+        <v>163</v>
       </c>
       <c r="F3" t="n">
-        <v>37</v>
+        <v>98</v>
       </c>
       <c r="G3" t="n">
-        <v>111</v>
+        <v>660</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>37.72</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>3090</v>
+        <v>47700</v>
       </c>
       <c r="K3" t="n">
-        <v>3190</v>
+        <v>51000</v>
       </c>
       <c r="L3" t="n">
-        <v>3400</v>
+        <v>56500</v>
       </c>
       <c r="M3" t="n">
-        <v>3155</v>
+        <v>50500</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>37.7</v>
       </c>
       <c r="O3" t="n">
-        <v>13692486478</v>
+        <v>353606002000</v>
       </c>
       <c r="P3" t="n">
-        <v>7050</v>
+        <v>67300</v>
       </c>
       <c r="Q3" t="n">
-        <v>2500</v>
+        <v>23150</v>
       </c>
       <c r="R3" t="n">
-        <v>12000</v>
+        <v>1440000</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>368000</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>김정은 신변 이상설 및 전쟁 가능성 고조에 따른 테마주로서 급등세를 보이며, 관련 뉴스와 함께 투기적 수요 유입.</t>
+          <t>실적 발표 어닝 서프라이즈, 주식 소각 결정, 전망 상향, 자사주 매입 공시 확인. 5000억 영업이익 달성.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['김정은 신변 이상설', '전쟁 테마', '급등']</t>
+          <t>['어닝 서프라이즈', '주식 소각', '자사주 매입']</t>
         </is>
       </c>
       <c r="X3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
@@ -740,90 +740,90 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>065450</t>
+          <t>028050</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>빅텍</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>15090</v>
+        <v>3320</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+2.17%</t>
+          <t>'+7.44%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.13</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="F4" t="n">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="G4" t="n">
-        <v>117</v>
+        <v>171</v>
       </c>
       <c r="H4" t="n">
-        <v>9.949999999999999</v>
+        <v>0</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>14770</v>
+        <v>3090</v>
       </c>
       <c r="K4" t="n">
-        <v>14770</v>
+        <v>3190</v>
       </c>
       <c r="L4" t="n">
-        <v>15290</v>
+        <v>3400</v>
       </c>
       <c r="M4" t="n">
-        <v>14770</v>
+        <v>3155</v>
       </c>
       <c r="N4" t="n">
-        <v>9.82</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>18122158975</v>
+        <v>14758276630</v>
       </c>
       <c r="P4" t="n">
-        <v>40350</v>
+        <v>7050</v>
       </c>
       <c r="Q4" t="n">
-        <v>3320</v>
+        <v>2500</v>
       </c>
       <c r="R4" t="n">
-        <v>-18000</v>
+        <v>12000</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>외국인 및 연기금의 꾸준한 매수세와 실적 우량주라는 언급이 있으나, 정치적 이슈 언급이 다수이며 주가 상승에 대한 명확한 근거 제시 부족.</t>
+          <t>김정은 신변 이상설 및 전쟁 가능성 부각. 빅텍 관련 언급 다수.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['외국인 매수', '실적 우량주', '정치적 이슈']</t>
+          <t>['김정은', '전쟁 가능성', '빅텍']</t>
         </is>
       </c>
       <c r="X4" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
@@ -832,7 +832,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>065450</t>
         </is>
       </c>
     </row>
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1637</v>
+        <v>1671</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+1.68%</t>
+          <t>'+3.79%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>-0.39</v>
       </c>
       <c r="E5" t="n">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="F5" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="G5" t="n">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="H5" t="n">
         <v>0.3</v>
@@ -886,7 +886,7 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="O5" t="n">
-        <v>5181946511</v>
+        <v>5629854206</v>
       </c>
       <c r="P5" t="n">
         <v>3980</v>
@@ -902,16 +902,16 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>이유 없는 하한가 두 번에 대한 의문 제기 및 주가 조작 의혹이 제기되며, 매각 불확정성 등 불확실성이 커 투자 심리 위축.</t>
+          <t>이유 없는 하한가 두 번에 대한 공시 답변 부재. 매각 관련 불확실성 속에 주가조작 의혹 제기.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['하한가', '주가 조작', '매각 불확정성']</t>
+          <t>['하한가', '공시', '매각']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>14520</v>
+        <v>14660</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+1.47%</t>
+          <t>'+2.45%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>0.33</v>
       </c>
       <c r="E6" t="n">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="F6" t="n">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="G6" t="n">
-        <v>187</v>
+        <v>215</v>
       </c>
       <c r="H6" t="n">
         <v>3.48</v>
@@ -969,7 +969,7 @@
         <v>14180</v>
       </c>
       <c r="L6" t="n">
-        <v>14650</v>
+        <v>14830</v>
       </c>
       <c r="M6" t="n">
         <v>13890</v>
@@ -978,7 +978,7 @@
         <v>3.15</v>
       </c>
       <c r="O6" t="n">
-        <v>37786996550</v>
+        <v>53332624805</v>
       </c>
       <c r="P6" t="n">
         <v>31500</v>
@@ -994,16 +994,16 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>엔비디아 AI 광통신 관련 글로벌 열풍 및 긍정적 뉴스 언급으로 인한 기대감이 형성되었으나, 나스닥 선물 변동성과 대차 잔고 부담으로 상승 동력 약화.</t>
+          <t>AI 광통신 열풍 및 EUV용 유리기판 제조 기술 확보 소식. 변동성 큰 흐름.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['AI 광통신', '엔비디아', '대차 잔고']</t>
+          <t>['AI 광통신', '유리기판', 'EUV']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1023,31 +1023,31 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>221500</v>
+        <v>15120</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'-0.89%</t>
+          <t>'+2.37%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.06</v>
+        <v>0.13</v>
       </c>
       <c r="E7" t="n">
-        <v>800</v>
+        <v>48</v>
       </c>
       <c r="F7" t="n">
-        <v>460</v>
+        <v>26</v>
       </c>
       <c r="G7" t="n">
-        <v>2877</v>
+        <v>122</v>
       </c>
       <c r="H7" t="n">
-        <v>46.14</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1055,47 +1055,47 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>223500</v>
+        <v>14770</v>
       </c>
       <c r="K7" t="n">
-        <v>221500</v>
+        <v>14770</v>
       </c>
       <c r="L7" t="n">
-        <v>226000</v>
+        <v>15290</v>
       </c>
       <c r="M7" t="n">
-        <v>220000</v>
+        <v>14770</v>
       </c>
       <c r="N7" t="n">
-        <v>46.08</v>
+        <v>9.82</v>
       </c>
       <c r="O7" t="n">
-        <v>553961994000</v>
+        <v>19835909225</v>
       </c>
       <c r="P7" t="n">
-        <v>374500</v>
+        <v>40350</v>
       </c>
       <c r="Q7" t="n">
-        <v>94500</v>
+        <v>3320</v>
       </c>
       <c r="R7" t="n">
-        <v>-54000</v>
+        <v>-95000</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>-14000</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>메타 호실적 및 AI 투자 확대 기대감과 달리, 반도체 섹터 전반의 혼조세 및 외국인 매매 패턴에 따라 변동성이 큰 모습을 보이며, 뚜렷한 방향성 없이 등락을 반복.</t>
+          <t>외국인 및 연기금 순매수 지속. 실적 우량주 언급되나, 정치적 메시지가 주를 이룸.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['AI 투자', '반도체 섹터', '외국인 매매']</t>
+          <t>['외국인 매수', '연기금', '실적 우량주']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1108,38 +1108,38 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>LG디스플레이</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>7250</v>
+        <v>223000</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'-1.36%</t>
+          <t>'-0.22%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.02</v>
+        <v>0.06</v>
       </c>
       <c r="E8" t="n">
-        <v>40</v>
+        <v>800</v>
       </c>
       <c r="F8" t="n">
-        <v>25</v>
+        <v>459</v>
       </c>
       <c r="G8" t="n">
-        <v>111</v>
+        <v>2735</v>
       </c>
       <c r="H8" t="n">
-        <v>25.47</v>
+        <v>46.14</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1147,51 +1147,51 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>7350</v>
+        <v>223500</v>
       </c>
       <c r="K8" t="n">
-        <v>7270</v>
+        <v>221500</v>
       </c>
       <c r="L8" t="n">
-        <v>7340</v>
+        <v>226000</v>
       </c>
       <c r="M8" t="n">
-        <v>7210</v>
+        <v>220000</v>
       </c>
       <c r="N8" t="n">
-        <v>25.45</v>
+        <v>46.08</v>
       </c>
       <c r="O8" t="n">
-        <v>3493800555</v>
+        <v>637071057250</v>
       </c>
       <c r="P8" t="n">
-        <v>17950</v>
+        <v>374500</v>
       </c>
       <c r="Q8" t="n">
-        <v>7190</v>
+        <v>94500</v>
       </c>
       <c r="R8" t="n">
-        <v>-20000</v>
+        <v>-89000</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>-156000</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>실적 발표에 따른 폭락 및 향후 전망에 대한 불확실성으로 투자 심리가 극도로 위축되었으며, PBR 지표와 기대감 언급에도 불구하고 매도 압력 지속.</t>
+          <t>메타 호실적 및 AI 투자 확대 기대감 속 반도체 수요 증가 전망. 다만, 국내 증시 흐름은 변동성이 큼.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['실적 발표', '향후 전망', 'PBR']</t>
+          <t>['AI 투자', '반도체', '메모리']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -1200,7 +1200,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>034220</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
@@ -1211,11 +1211,11 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1276000</v>
+        <v>1285000</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'-1.39%</t>
+          <t>'-0.70%</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -1225,10 +1225,10 @@
         <v>800</v>
       </c>
       <c r="F9" t="n">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="G9" t="n">
-        <v>2008</v>
+        <v>1979</v>
       </c>
       <c r="H9" t="n">
         <v>48.79</v>
@@ -1254,7 +1254,7 @@
         <v>48.77</v>
       </c>
       <c r="O9" t="n">
-        <v>662249335000</v>
+        <v>792157062500</v>
       </c>
       <c r="P9" t="n">
         <v>2987000</v>
@@ -1263,23 +1263,23 @@
         <v>468000</v>
       </c>
       <c r="R9" t="n">
-        <v>-2000</v>
+        <v>-36000</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>자사주 매입 종료와 미국장 반도체 주가 변동성에 대한 우려, 정치적 리스크 언급 등으로 인해 투자 심리가 위축되며 하락세를 보이고, 뚜렷한 호재 부재.</t>
+          <t>자사주 매입 종료 이후 주가 하락 우려. 기업 윤리 및 경영진에 대한 부정적 언급.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['자사주 매입 종료', '반도체 주가', '정치적 리스크']</t>
+          <t>['자사주 매입', '기업 윤리', '주가 하락']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1299,83 +1299,83 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>HLB</t>
+          <t>LG디스플레이</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>41450</v>
+        <v>7260</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'-2.13%</t>
+          <t>'-1.22%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-0.14</v>
+        <v>0.02</v>
       </c>
       <c r="E10" t="n">
-        <v>97</v>
+        <v>43</v>
       </c>
       <c r="F10" t="n">
-        <v>59</v>
+        <v>26</v>
       </c>
       <c r="G10" t="n">
-        <v>431</v>
+        <v>123</v>
       </c>
       <c r="H10" t="n">
-        <v>13.09</v>
+        <v>25.47</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>42350</v>
+        <v>7350</v>
       </c>
       <c r="K10" t="n">
-        <v>41850</v>
+        <v>7270</v>
       </c>
       <c r="L10" t="n">
-        <v>42350</v>
+        <v>7340</v>
       </c>
       <c r="M10" t="n">
-        <v>41150</v>
+        <v>7210</v>
       </c>
       <c r="N10" t="n">
-        <v>13.23</v>
+        <v>25.45</v>
       </c>
       <c r="O10" t="n">
-        <v>4406933325</v>
+        <v>4031089250</v>
       </c>
       <c r="P10" t="n">
-        <v>69200</v>
+        <v>17950</v>
       </c>
       <c r="Q10" t="n">
-        <v>24150</v>
+        <v>7190</v>
       </c>
       <c r="R10" t="n">
-        <v>-1000</v>
+        <v>-47000</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>-18000</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>HLB, 간암 치료제 FDA 승인 기대감 및 공매도 관련 논의. 기관 수급 및 C1/C2 관련 분석.</t>
+          <t>실적 발표 예정. PBR 0.57 언급. OLED 관련 뉴스 및 TV 사업 전망.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.5</v>
+        <v>0.1</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['FDA 승인', '간암 치료제', '공매도']</t>
+          <t>['실적 발표', 'PBR', 'OLED']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1384,90 +1384,90 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>028300</t>
+          <t>034220</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>명신산업</t>
+          <t>HLB</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>9820</v>
+        <v>41700</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-3.63%</t>
+          <t>'-1.53%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.53</v>
+        <v>-0.14</v>
       </c>
       <c r="E11" t="n">
-        <v>84</v>
+        <v>103</v>
       </c>
       <c r="F11" t="n">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="G11" t="n">
-        <v>242</v>
+        <v>435</v>
       </c>
       <c r="H11" t="n">
-        <v>5.87</v>
+        <v>13.09</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>10190</v>
+        <v>42350</v>
       </c>
       <c r="K11" t="n">
-        <v>10110</v>
+        <v>41850</v>
       </c>
       <c r="L11" t="n">
-        <v>10180</v>
+        <v>42350</v>
       </c>
       <c r="M11" t="n">
-        <v>9720</v>
+        <v>41150</v>
       </c>
       <c r="N11" t="n">
-        <v>5.34</v>
+        <v>13.23</v>
       </c>
       <c r="O11" t="n">
-        <v>7349378405</v>
+        <v>5074099125</v>
       </c>
       <c r="P11" t="n">
-        <v>14940</v>
+        <v>69200</v>
       </c>
       <c r="Q11" t="n">
-        <v>5390</v>
+        <v>24150</v>
       </c>
       <c r="R11" t="n">
-        <v>-45000</v>
+        <v>-1000</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>테슬라 실적 상회 및 스페이스X 상장 이슈 등 긍정적 재료 언급에도 불구하고, 공매도 압박 및 변동성 심화로 인해 하락세를 보이며 투자 심리 위축.</t>
+          <t>FDA 간암 치료제 승인 기대감 속 기관 수급 확인. 임상 3상 결과 및 승인 여부에 대한 불확실성 존재.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['테슬라 실적', '공매도', '변동성']</t>
+          <t>['FDA', '간암', '승인']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1476,97 +1476,189 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>009900</t>
+          <t>028300</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>HT로보틱스</t>
+          <t>명신산업</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>10340</v>
+        <v>9950</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-7.18%</t>
+          <t>'-2.36%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>2.41</v>
+        <v>0.53</v>
       </c>
       <c r="E12" t="n">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="F12" t="n">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G12" t="n">
-        <v>250</v>
+        <v>244</v>
       </c>
       <c r="H12" t="n">
-        <v>3.69</v>
+        <v>5.87</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>11140</v>
+        <v>10190</v>
       </c>
       <c r="K12" t="n">
-        <v>10830</v>
+        <v>10110</v>
       </c>
       <c r="L12" t="n">
-        <v>10880</v>
+        <v>10180</v>
       </c>
       <c r="M12" t="n">
-        <v>10050</v>
+        <v>9720</v>
       </c>
       <c r="N12" t="n">
-        <v>1.28</v>
+        <v>5.34</v>
       </c>
       <c r="O12" t="n">
-        <v>31457845550</v>
+        <v>8165304355</v>
       </c>
       <c r="P12" t="n">
-        <v>11690</v>
+        <v>14940</v>
       </c>
       <c r="Q12" t="n">
-        <v>2270</v>
+        <v>5390</v>
       </c>
       <c r="R12" t="n">
-        <v>-34000</v>
+        <v>-84000</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>로봇주 Nxt 시장 폭등 기대감에도 불구하고, 예상치 못한 투기 과열 지정 및 ESS 마진율 불확실성 등으로 급락하며 투자 심리 급랭.</t>
+          <t>테슬라 실적 상회 및 스페이스X 상장 이슈 언급. 공매도에 대한 언급 다수.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['로봇주', '투기 과열', 'ESS 마진율']</t>
+          <t>['테슬라', '스페이스X', '공매도']</t>
         </is>
       </c>
       <c r="X12" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>009900</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>HT로보틱스</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>10370</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>'-6.91%</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="E13" t="n">
+        <v>92</v>
+      </c>
+      <c r="F13" t="n">
+        <v>58</v>
+      </c>
+      <c r="G13" t="n">
+        <v>255</v>
+      </c>
+      <c r="H13" t="n">
+        <v>3.69</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>11140</v>
+      </c>
+      <c r="K13" t="n">
+        <v>10830</v>
+      </c>
+      <c r="L13" t="n">
+        <v>10880</v>
+      </c>
+      <c r="M13" t="n">
+        <v>10050</v>
+      </c>
+      <c r="N13" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="O13" t="n">
+        <v>34360997715</v>
+      </c>
+      <c r="P13" t="n">
+        <v>11690</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>2270</v>
+      </c>
+      <c r="R13" t="n">
+        <v>-34000</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> NXT 시장 로봇주 폭등 언급. 투기 과열 종목 지정 및 급락 예상.</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr"/>
+      <c r="V13" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>['로봇주', 'nxt', '투기과열']</t>
+        </is>
+      </c>
+      <c r="X13" t="n">
         <v>5</v>
       </c>
-      <c r="Y12" t="inlineStr">
+      <c r="Y13" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
+      <c r="Z13" t="inlineStr">
         <is>
           <t>396300</t>
         </is>
